--- a/tools/importer/reports/import-product.report.xlsx
+++ b/tools/importer/reports/import-product.report.xlsx
@@ -70,7 +70,7 @@
     <t>product/detail-1218</t>
   </si>
   <si>
-    <t>2026-10-05T14:21:31.029Z</t>
+    <t>2026-10-05T14:37:32.048Z</t>
   </si>
   <si>
     <t>PDRN 볼륨 두피 헤어팩 - 닥터그루트 공식 온라인 스토어</t>
